--- a/Employee_Reports_wi48/Mohamed Faizal Mohamed Uvais Q0493.xlsx
+++ b/Employee_Reports_wi48/Mohamed Faizal Mohamed Uvais Q0493.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-283</v>
+        <v>-286</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1336,9 +1336,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>05-Apr-2025</t>
@@ -1350,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-99</v>
+        <v>-102</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1399,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-99</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1448,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1497,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1546,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1595,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1644,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1681,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1718,11 +1730,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2265,7 +2277,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2288,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2360,7 +2372,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2389,7 +2401,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2418,7 +2430,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2447,7 +2459,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2488,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2505,7 +2517,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2534,7 +2546,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7946</v>
+        <v>7943</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2542,6 +2554,151 @@
         </is>
       </c>
       <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 20ft</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 15ft</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 20ft</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 15ft</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
